--- a/data/externalStats/File1/RPT_RPT6724285789423RU_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT6724285789423RU_externalStats.xlsx
@@ -2104,7 +2104,7 @@
         <v>28321869.63325635</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>37842.22928475848</v>
+        <v>37842.22928475847</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>10257140.96843845</v>
+        <v>10257140.96843846</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>12396.8159518388</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>9804357.984809292</v>
+        <v>9804357.984809294</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>487.1813100000001</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>7349724.884596497</v>
+        <v>7349724.884596495</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>563.805105</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>6188704.374589607</v>
+        <v>6188704.374589608</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>3352.283312</v>
@@ -2623,7 +2623,7 @@
         <v>5634318.814640129</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>752.3329949999999</v>
+        <v>752.332995</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5231411.651656953</v>
+        <v>5231411.651656954</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>780.9839425823878</v>
+        <v>780.9839425823877</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>2901313.69343935</v>
+        <v>2901313.693439351</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>354.0840958925123</v>
+        <v>354.0840958925122</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -3697,7 +3697,7 @@
         <v>49532560.644583</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>6670.893598846876</v>
+        <v>6670.893598846875</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -3713,7 +3713,7 @@
         <v>42381311.56098315</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>56332.87391490716</v>
+        <v>56332.87391490715</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -3726,22 +3726,28 @@
       <c r="F51" s="12" t="n"/>
       <c r="G51" s="13" t="n"/>
       <c r="H51" s="14" t="n"/>
-      <c r="J51" s="11" t="n">
-        <v>2027</v>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
       </c>
       <c r="K51" s="12" t="n"/>
       <c r="L51" s="12" t="n"/>
       <c r="M51" s="13" t="n"/>
       <c r="N51" s="14" t="n"/>
-      <c r="P51" s="11" t="n">
-        <v>2028</v>
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
       </c>
       <c r="Q51" s="12" t="n"/>
       <c r="R51" s="12" t="n"/>
       <c r="S51" s="13" t="n"/>
       <c r="T51" s="14" t="n"/>
-      <c r="V51" s="11" t="n">
-        <v>2029</v>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
       </c>
       <c r="W51" s="12" t="n"/>
       <c r="X51" s="12" t="n"/>
@@ -3759,7 +3765,7 @@
         <v>11233059.35150177</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>13939.77200165374</v>
+        <v>13939.77200165373</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -3877,7 +3883,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>8567448.901922544</v>
+        <v>8567448.901922543</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>10800.2529744</v>
@@ -4039,7 +4045,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>7802523.646432152</v>
+        <v>7802523.646432151</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>4030.61368395</v>
@@ -4123,7 +4129,7 @@
         <v>3515960.911042318</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>9565.774205806498</v>
+        <v>9565.774205806496</v>
       </c>
     </row>
     <row r="56">
@@ -4204,7 +4210,7 @@
         <v>2557001.206573612</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>6706.464778411767</v>
+        <v>6706.464778411768</v>
       </c>
     </row>
     <row r="57">
@@ -4322,13 +4328,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5043.97753572962</v>
+        <v>5043.977535729621</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>3672.153688237323</v>
+        <v>3672.153688237326</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1178.733620422441</v>
+        <v>1178.73362042244</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>276.6926051831596</v>
@@ -4337,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842924</v>
+        <v>5127.579913842926</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>3728.347202327301</v>
@@ -4352,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077948</v>
+        <v>5217.744981077949</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -4397,7 +4403,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
         <v>4111.798092690687</v>
@@ -4412,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.5777408532682</v>
+        <v>405.5777408532681</v>
       </c>
       <c r="S59" s="131" t="n">
         <v>4497.071348597412</v>
@@ -4444,10 +4450,10 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1652160.935343547</v>
+        <v>1652160.935343546</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>4793.408093083508</v>
+        <v>4793.408093083509</v>
       </c>
     </row>
     <row r="60">
@@ -4556,10 +4562,10 @@
         <v>2710.474833260433</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.0358767901117</v>
+        <v>710.0358767901118</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>227.8577587891603</v>
+        <v>227.8577587891604</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>549.7124589894161</v>
@@ -4571,31 +4577,31 @@
         <v>2848.462218149934</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>760.0653829141094</v>
+        <v>760.0653829141091</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>237.7472517739969</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193557</v>
+        <v>560.6592858193558</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4406.934138657395</v>
+        <v>4406.934138657396</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>3005.608292870229</v>
+        <v>3005.608292870228</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.249027688854</v>
+        <v>816.2490276888542</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.3087850252182</v>
+        <v>582.308785025218</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4652.87302083473</v>
+        <v>4652.873020834729</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -4715,34 +4721,34 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862917</v>
+        <v>2315.01722486291</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>410.0571917407924</v>
+        <v>410.0571917407915</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.7306729614256</v>
+        <v>140.7306729614252</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>4860.049068810829</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375964</v>
+        <v>7725.854158375956</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303845</v>
+        <v>2462.596460303837</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224293</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>151.8055148266708</v>
+        <v>151.8055148266703</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>5497.21023131672</v>
+        <v>5497.210231316722</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.617991469664</v>
+        <v>8533.617991469659</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>2639.658250704611</v>
@@ -4754,10 +4760,10 @@
         <v>165.5077469208077</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865837</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292729</v>
+        <v>9544.249776292727</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -5020,7 +5026,7 @@
         <v>1004640.073337914</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>4489.79398771465</v>
+        <v>4489.793987714651</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -5045,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>31870.3334309905</v>
+        <v>31870.33343099051</v>
       </c>
       <c r="K67" s="140" t="n">
         <v>4029.79567811647</v>
@@ -5054,16 +5060,16 @@
         <v>1407.005950657853</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>3375.286604353636</v>
+        <v>3375.286604353637</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>40682.42166411846</v>
+        <v>40682.42166411847</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>32493.07951996083</v>
+        <v>32493.07951996084</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>4092.276733052207</v>
+        <v>4092.276733052206</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>1367.292909233702</v>
@@ -5075,19 +5081,19 @@
         <v>41401.49046288215</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4402.675607700118</v>
+        <v>4402.67560770012</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>3796.051969460276</v>
+        <v>3796.051969460277</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -5098,7 +5104,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>989013.90751893</v>
+        <v>989013.9075189302</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>2740.1603206045</v>
@@ -5141,10 +5147,10 @@
         <v>62122.69724342013</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665193</v>
+        <v>41476.29188665194</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>6453.081521411186</v>
+        <v>6453.081521411184</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>2439.116021870797</v>
@@ -5153,13 +5159,13 @@
         <v>14003.78216636889</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>64372.27159630281</v>
+        <v>64372.27159630282</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906604</v>
+        <v>43398.71923906603</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>6878.522835275836</v>
+        <v>6878.522835275839</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>2535.996836477477</v>
@@ -5168,7 +5174,7 @@
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.35109118339</v>
+        <v>68414.35109118337</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -5686,10 +5692,10 @@
         <v>183.3291939762258</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641998</v>
+        <v>131.7328156641999</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399727</v>
+        <v>44.13439203399725</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -5701,10 +5707,10 @@
         <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
-        <v>134.4005706694529</v>
+        <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.0557720216745</v>
+        <v>45.05577202167449</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -5713,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="Z76" s="132" t="n">
-        <v>192.1638534700123</v>
+        <v>192.1638534700124</v>
       </c>
     </row>
     <row r="77">
@@ -5744,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="131" t="n">
-        <v>46.76991949101995</v>
+        <v>46.76991949101996</v>
       </c>
       <c r="M77" s="131" t="n">
         <v>311.9992424177221</v>
@@ -5759,13 +5765,13 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.04086451328254</v>
+        <v>51.04086451328255</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>377.5567550856683</v>
+        <v>377.5567550856682</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>428.5976195989509</v>
+        <v>428.5976195989508</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -5774,13 +5780,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91560864239314</v>
+        <v>55.91560864239312</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>486.2580302793615</v>
+        <v>486.2580302793614</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>542.1736389217547</v>
+        <v>542.1736389217546</v>
       </c>
     </row>
     <row r="78">
@@ -5890,10 +5896,10 @@
         <v>2967.818385277548</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780187</v>
+        <v>141.3309685780186</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88229397936017</v>
+        <v>62.88229397936021</v>
       </c>
       <c r="S79" s="131" t="n">
         <v>11.02028858145198</v>
@@ -5908,7 +5914,7 @@
         <v>170.8985703395071</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.00721802598373</v>
+        <v>73.00721802598372</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>11.21257820469615</v>
@@ -6030,10 +6036,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>1478.163076655088</v>
+        <v>1478.163076655087</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>1478.163076655088</v>
+        <v>1478.163076655087</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>0</v>
@@ -6278,49 +6284,49 @@
         <v>0</v>
       </c>
       <c r="J85" s="139" t="n">
-        <v>1104024.706418759</v>
+        <v>1104024.70641876</v>
       </c>
       <c r="K85" s="140" t="n">
-        <v>251028.9710893382</v>
+        <v>251028.9710893376</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57255.12843901187</v>
+        <v>57255.12843901185</v>
       </c>
       <c r="M85" s="140" t="n">
-        <v>1196.145206488663</v>
+        <v>1196.145206488664</v>
       </c>
       <c r="N85" s="141" t="n">
         <v>1413504.951153598</v>
       </c>
       <c r="P85" s="139" t="n">
-        <v>1115926.625891631</v>
+        <v>1115926.625891636</v>
       </c>
       <c r="Q85" s="140" t="n">
-        <v>252563.5334183742</v>
+        <v>252563.5334183738</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>57807.83114897597</v>
+        <v>57807.83114897595</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1395.789484341962</v>
+        <v>1395.789484341961</v>
       </c>
       <c r="T85" s="141" t="n">
-        <v>1427693.779943323</v>
+        <v>1427693.779943328</v>
       </c>
       <c r="V85" s="139" t="n">
-        <v>1125670.849041048</v>
+        <v>1125670.849041047</v>
       </c>
       <c r="W85" s="140" t="n">
-        <v>253578.7535428638</v>
+        <v>253578.7535428643</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>58272.40781879693</v>
+        <v>58272.40781879695</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>1540.766409614355</v>
       </c>
       <c r="Z85" s="141" t="n">
-        <v>1439062.776812323</v>
+        <v>1439062.776812322</v>
       </c>
     </row>
     <row r="86" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -6345,13 +6351,13 @@
         <v>3478</v>
       </c>
       <c r="J86" s="142" t="n">
-        <v>1106850.058062584</v>
+        <v>1106850.058062585</v>
       </c>
       <c r="K86" s="143" t="n">
-        <v>251183.7261189914</v>
+        <v>251183.7261189908</v>
       </c>
       <c r="L86" s="143" t="n">
-        <v>57365.21870971905</v>
+        <v>57365.21870971904</v>
       </c>
       <c r="M86" s="143" t="n">
         <v>2922.954135118953</v>
@@ -6360,31 +6366,31 @@
         <v>1418321.957026413</v>
       </c>
       <c r="P86" s="142" t="n">
-        <v>1119026.177092572</v>
+        <v>1119026.177092578</v>
       </c>
       <c r="Q86" s="143" t="n">
-        <v>252748.9987789862</v>
+        <v>252748.9987789859</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>57934.20212323379</v>
+        <v>57934.20212323377</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>3262.52960466417</v>
+        <v>3262.529604664169</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>1432971.907599456</v>
+        <v>1432971.907599461</v>
       </c>
       <c r="V86" s="142" t="n">
-        <v>1129050.297315568</v>
+        <v>1129050.297315567</v>
       </c>
       <c r="W86" s="143" t="n">
-        <v>253794.707885225</v>
+        <v>253794.7078852255</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58414.03815624419</v>
+        <v>58414.03815624421</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>3611.957540811319</v>
+        <v>3611.957540811318</v>
       </c>
       <c r="Z86" s="144" t="n">
         <v>1444871.000897848</v>
@@ -6882,7 +6888,7 @@
         <v>1189.94975831014</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>287.3141106471616</v>
+        <v>287.3141106471617</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -6891,7 +6897,7 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901523</v>
+        <v>3803.886503901525</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
@@ -6903,22 +6909,22 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>5315.894937306298</v>
+        <v>5315.8949373063</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1256.376585107065</v>
+        <v>1256.376585107066</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5409.908834547959</v>
+        <v>5409.90883454796</v>
       </c>
     </row>
     <row r="95">
@@ -6949,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>407.3347841672957</v>
+        <v>407.3347841672958</v>
       </c>
       <c r="M95" s="131" t="n">
         <v>4423.797335108409</v>
@@ -6964,7 +6970,7 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665507</v>
+        <v>456.6186053665506</v>
       </c>
       <c r="S95" s="131" t="n">
         <v>4874.628103683081</v>
@@ -7080,10 +7086,10 @@
         <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>821.8541182771896</v>
+        <v>821.8541182771897</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>279.0679125332354</v>
+        <v>279.0679125332355</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>560.6457744410619</v>
@@ -7092,34 +7098,34 @@
         <v>7069.112073998887</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5816.280603427482</v>
+        <v>5816.280603427483</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.396351492128</v>
+        <v>901.3963514921277</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>300.6295457533571</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008076</v>
+        <v>571.6795744008077</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7589.986075073774</v>
+        <v>7589.986075073775</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.655996720889</v>
+        <v>6250.655996720888</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>987.1475980283611</v>
+        <v>987.1475980283614</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>321.7141332764122</v>
+        <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299143</v>
+        <v>593.5213632299141</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8153.039091255577</v>
+        <v>8153.039091255575</v>
       </c>
     </row>
     <row r="98">
@@ -7235,25 +7241,25 @@
         <v>151.8055148266722</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>6975.373307971806</v>
+        <v>6975.373307971811</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>10011.78106812466</v>
+        <v>10011.78106812467</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2639.658250704873</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>448.277386801492</v>
+        <v>448.2773868014629</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578742</v>
+        <v>7864.526914578741</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>11117.97029900591</v>
+        <v>11117.97029900588</v>
       </c>
     </row>
     <row r="100">
@@ -7486,40 +7492,40 @@
         <v>1135895.03984975</v>
       </c>
       <c r="K103" s="140" t="n">
-        <v>255058.7667674547</v>
+        <v>255058.7667674541</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58662.13438966972</v>
+        <v>58662.13438966971</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>4571.431810842299</v>
+        <v>4571.431810842301</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>1454187.372817716</v>
       </c>
       <c r="P103" s="139" t="n">
-        <v>1148419.705411591</v>
+        <v>1148419.705411597</v>
       </c>
       <c r="Q103" s="140" t="n">
-        <v>256655.8101514264</v>
+        <v>256655.8101514261</v>
       </c>
       <c r="R103" s="140" t="n">
-        <v>59175.12405820967</v>
+        <v>59175.12405820965</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>4844.630784977365</v>
+        <v>4844.630784977364</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>1469095.270406205</v>
+        <v>1469095.27040621</v>
       </c>
       <c r="V103" s="139" t="n">
-        <v>1159695.954534212</v>
+        <v>1159695.95453421</v>
       </c>
       <c r="W103" s="140" t="n">
-        <v>257981.4291505639</v>
+        <v>257981.4291505645</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>59655.70951589625</v>
+        <v>59655.70951589627</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>5336.818379074632</v>
@@ -7550,13 +7556,13 @@
         <v>48702</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1147367.644204108</v>
+        <v>1147367.644204109</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>257480.6278357828</v>
+        <v>257480.6278357822</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>59776.58186997884</v>
+        <v>59776.58186997882</v>
       </c>
       <c r="M104" s="143" t="n">
         <v>15819.80035996352</v>
@@ -7565,34 +7571,34 @@
         <v>1480444.654269833</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1160502.468979224</v>
+        <v>1160502.468979229</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>259202.0803003974</v>
+        <v>259202.0803003971</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>60373.31814510459</v>
+        <v>60373.31814510457</v>
       </c>
       <c r="S104" s="143" t="n">
         <v>17266.31177103306</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1497344.179195759</v>
+        <v>1497344.179195764</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1172449.016554634</v>
+        <v>1172449.016554633</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>260673.2307205008</v>
+        <v>260673.2307205013</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>60950.03499272167</v>
+        <v>60950.03499272169</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>19213.06972117535</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1513285.351989032</v>
+        <v>1513285.351989031</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -8721,7 +8727,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>1518.116782665446</v>
+        <v>1518.116782665447</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -8782,7 +8788,7 @@
         <v>11601907.67586606</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>13973.95203328434</v>
+        <v>13973.95203328433</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -8936,7 +8942,7 @@
         <v>10130759.10811187</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>496.3110877493999</v>
+        <v>496.3110877494</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -9010,7 +9016,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>9576725.592281304</v>
+        <v>9576725.592281302</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>683.1908359837499</v>
@@ -9144,7 +9150,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>7261041.493413352</v>
+        <v>7261041.493413353</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>911.6395066912501</v>
@@ -9221,10 +9227,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5596493.161870113</v>
+        <v>5596493.161870114</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>795.784626769313</v>
+        <v>795.7846267693131</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -9301,7 +9307,7 @@
         <v>5451507.926517456</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>10927.57377472859</v>
+        <v>10927.57377472858</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -9455,7 +9461,7 @@
         <v>3129242.204697554</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>360.8044705626896</v>
+        <v>360.8044705626895</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -9672,7 +9678,7 @@
         <v>2065048.249427686</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>386.7359125319999</v>
+        <v>386.735912532</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -9893,7 +9899,7 @@
         <v>1751703.99415768</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>2220.603683210644</v>
+        <v>2220.603683210645</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -9909,7 +9915,7 @@
         </is>
       </c>
       <c r="AN42" s="58" t="n">
-        <v>337.2342832499999</v>
+        <v>337.23428325</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" thickBot="1">
@@ -10250,22 +10256,28 @@
       <c r="F51" s="12" t="n"/>
       <c r="G51" s="13" t="n"/>
       <c r="H51" s="14" t="n"/>
-      <c r="J51" s="11" t="n">
-        <v>2028</v>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
       </c>
       <c r="K51" s="12" t="n"/>
       <c r="L51" s="12" t="n"/>
       <c r="M51" s="13" t="n"/>
       <c r="N51" s="14" t="n"/>
-      <c r="P51" s="11" t="n">
-        <v>2028</v>
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
       </c>
       <c r="Q51" s="12" t="n"/>
       <c r="R51" s="12" t="n"/>
       <c r="S51" s="13" t="n"/>
       <c r="T51" s="14" t="n"/>
-      <c r="V51" s="11" t="n">
-        <v>2029</v>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
       </c>
       <c r="W51" s="12" t="n"/>
       <c r="X51" s="12" t="n"/>
@@ -10644,7 +10656,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>3761546.093803572</v>
+        <v>3761546.093803573</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>10006.56508121006</v>
@@ -10728,7 +10740,7 @@
         <v>2908992.67724763</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>250.2622030851889</v>
+        <v>250.2622030851888</v>
       </c>
     </row>
     <row r="57">
@@ -10846,13 +10858,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5043.97753572962</v>
+        <v>5043.977535729621</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>3672.153688237323</v>
+        <v>3672.153688237326</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1178.733620422441</v>
+        <v>1178.73362042244</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>276.6926051831596</v>
@@ -10861,7 +10873,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842924</v>
+        <v>5127.579913842926</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>3728.347202327301</v>
@@ -10876,7 +10888,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077948</v>
+        <v>5217.744981077949</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -10921,7 +10933,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
         <v>4111.798092690687</v>
@@ -10936,7 +10948,7 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.5777408532682</v>
+        <v>405.5777408532681</v>
       </c>
       <c r="S59" s="131" t="n">
         <v>4497.071348597412</v>
@@ -10968,7 +10980,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1650870.480105934</v>
+        <v>1650870.480105933</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>4575.883233819379</v>
@@ -11049,7 +11061,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1612181.54885225</v>
+        <v>1612181.548852249</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>0</v>
@@ -11080,10 +11092,10 @@
         <v>2710.474833260433</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.0358767901117</v>
+        <v>710.0358767901118</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>227.8577587891603</v>
+        <v>227.8577587891604</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>549.7124589894161</v>
@@ -11095,31 +11107,31 @@
         <v>2848.462218149934</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>760.0653829141094</v>
+        <v>760.0653829141091</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>237.7472517739969</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193557</v>
+        <v>560.6592858193558</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4406.934138657395</v>
+        <v>4406.934138657396</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>3005.608292870229</v>
+        <v>3005.608292870228</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.249027688854</v>
+        <v>816.2490276888542</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.3087850252182</v>
+        <v>582.308785025218</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4652.87302083473</v>
+        <v>4652.873020834729</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -11239,34 +11251,34 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862917</v>
+        <v>2315.01722486291</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>410.0571917407924</v>
+        <v>410.0571917407915</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.7306729614256</v>
+        <v>140.7306729614252</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>4860.049068810829</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375964</v>
+        <v>7725.854158375956</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303845</v>
+        <v>2462.596460303837</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224293</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>151.8055148266708</v>
+        <v>151.8055148266703</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>5497.21023131672</v>
+        <v>5497.210231316722</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.617991469664</v>
+        <v>8533.617991469659</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>2639.658250704611</v>
@@ -11278,10 +11290,10 @@
         <v>165.5077469208077</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865837</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292729</v>
+        <v>9544.249776292727</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11544,7 +11556,7 @@
         <v>1033276.645450031</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>4601.051082730221</v>
+        <v>4601.05108273022</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -11569,7 +11581,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>31870.3334309905</v>
+        <v>31870.33343099051</v>
       </c>
       <c r="K67" s="140" t="n">
         <v>4029.79567811647</v>
@@ -11578,16 +11590,16 @@
         <v>1407.005950657853</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>3375.286604353636</v>
+        <v>3375.286604353637</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>40682.42166411846</v>
+        <v>40682.42166411847</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>32493.07951996083</v>
+        <v>32493.07951996084</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>4092.276733052207</v>
+        <v>4092.276733052206</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>1367.292909233702</v>
@@ -11599,19 +11611,19 @@
         <v>41401.49046288215</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4402.675607700118</v>
+        <v>4402.67560770012</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>3796.051969460276</v>
+        <v>3796.051969460277</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -11622,7 +11634,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>843352.6226514207</v>
+        <v>843352.6226514205</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>2581.255131689318</v>
@@ -11665,10 +11677,10 @@
         <v>62122.69724342013</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665193</v>
+        <v>41476.29188665194</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>6453.081521411186</v>
+        <v>6453.081521411184</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>2439.116021870797</v>
@@ -11677,13 +11689,13 @@
         <v>14003.78216636889</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>64372.27159630281</v>
+        <v>64372.27159630282</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906604</v>
+        <v>43398.71923906603</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>6878.522835275836</v>
+        <v>6878.522835275839</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>2535.996836477477</v>
@@ -11692,7 +11704,7 @@
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.35109118339</v>
+        <v>68414.35109118337</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -11703,7 +11715,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>766273.5453469638</v>
+        <v>766273.5453469639</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>509.1231169767389</v>
@@ -12210,10 +12222,10 @@
         <v>183.3291939762258</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641998</v>
+        <v>131.7328156641999</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399727</v>
+        <v>44.13439203399725</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -12225,10 +12237,10 @@
         <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
-        <v>134.4005706694529</v>
+        <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.0557720216745</v>
+        <v>45.05577202167449</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -12237,7 +12249,7 @@
         <v>0</v>
       </c>
       <c r="Z76" s="132" t="n">
-        <v>192.1638534700123</v>
+        <v>192.1638534700124</v>
       </c>
     </row>
     <row r="77">
@@ -12268,7 +12280,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="131" t="n">
-        <v>46.76991949101995</v>
+        <v>46.76991949101996</v>
       </c>
       <c r="M77" s="131" t="n">
         <v>311.9992424177221</v>
@@ -12283,13 +12295,13 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.04086451328254</v>
+        <v>51.04086451328255</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>377.5567550856683</v>
+        <v>377.5567550856682</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>428.5976195989509</v>
+        <v>428.5976195989508</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -12298,13 +12310,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91560864239314</v>
+        <v>55.91560864239312</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>486.2580302793615</v>
+        <v>486.2580302793614</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>542.1736389217547</v>
+        <v>542.1736389217546</v>
       </c>
     </row>
     <row r="78">
@@ -12414,10 +12426,10 @@
         <v>2967.818385277548</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780187</v>
+        <v>141.3309685780186</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88229397936017</v>
+        <v>62.88229397936021</v>
       </c>
       <c r="S79" s="131" t="n">
         <v>11.02028858145198</v>
@@ -12432,7 +12444,7 @@
         <v>170.8985703395071</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.00721802598373</v>
+        <v>73.00721802598372</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>11.21257820469615</v>
@@ -12554,10 +12566,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>1478.163076655088</v>
+        <v>1478.163076655087</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>1478.163076655088</v>
+        <v>1478.163076655087</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>0</v>
@@ -12802,49 +12814,49 @@
         <v>0</v>
       </c>
       <c r="J85" s="139" t="n">
-        <v>1104024.706418759</v>
+        <v>1104024.70641876</v>
       </c>
       <c r="K85" s="140" t="n">
-        <v>251028.9710893382</v>
+        <v>251028.9710893376</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57255.12843901187</v>
+        <v>57255.12843901185</v>
       </c>
       <c r="M85" s="140" t="n">
-        <v>1196.145206488663</v>
+        <v>1196.145206488664</v>
       </c>
       <c r="N85" s="141" t="n">
         <v>1413504.951153598</v>
       </c>
       <c r="P85" s="139" t="n">
-        <v>1115926.625891631</v>
+        <v>1115926.625891636</v>
       </c>
       <c r="Q85" s="140" t="n">
-        <v>252563.5334183742</v>
+        <v>252563.5334183738</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>57807.83114897597</v>
+        <v>57807.83114897595</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1395.789484341962</v>
+        <v>1395.789484341961</v>
       </c>
       <c r="T85" s="141" t="n">
-        <v>1427693.779943323</v>
+        <v>1427693.779943328</v>
       </c>
       <c r="V85" s="139" t="n">
-        <v>1125670.849041048</v>
+        <v>1125670.849041047</v>
       </c>
       <c r="W85" s="140" t="n">
-        <v>253578.7535428638</v>
+        <v>253578.7535428643</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>58272.40781879693</v>
+        <v>58272.40781879695</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>1540.766409614355</v>
       </c>
       <c r="Z85" s="141" t="n">
-        <v>1439062.776812323</v>
+        <v>1439062.776812322</v>
       </c>
     </row>
     <row r="86" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -12869,13 +12881,13 @@
         <v>3478</v>
       </c>
       <c r="J86" s="142" t="n">
-        <v>1106850.058062584</v>
+        <v>1106850.058062585</v>
       </c>
       <c r="K86" s="143" t="n">
-        <v>251183.7261189914</v>
+        <v>251183.7261189908</v>
       </c>
       <c r="L86" s="143" t="n">
-        <v>57365.21870971905</v>
+        <v>57365.21870971904</v>
       </c>
       <c r="M86" s="143" t="n">
         <v>2922.954135118953</v>
@@ -12884,31 +12896,31 @@
         <v>1418321.957026413</v>
       </c>
       <c r="P86" s="142" t="n">
-        <v>1119026.177092572</v>
+        <v>1119026.177092578</v>
       </c>
       <c r="Q86" s="143" t="n">
-        <v>252748.9987789862</v>
+        <v>252748.9987789859</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>57934.20212323379</v>
+        <v>57934.20212323377</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>3262.52960466417</v>
+        <v>3262.529604664169</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>1432971.907599456</v>
+        <v>1432971.907599461</v>
       </c>
       <c r="V86" s="142" t="n">
-        <v>1129050.297315568</v>
+        <v>1129050.297315567</v>
       </c>
       <c r="W86" s="143" t="n">
-        <v>253794.707885225</v>
+        <v>253794.7078852255</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58414.03815624419</v>
+        <v>58414.03815624421</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>3611.957540811319</v>
+        <v>3611.957540811318</v>
       </c>
       <c r="Z86" s="144" t="n">
         <v>1444871.000897848</v>
@@ -13406,7 +13418,7 @@
         <v>1189.94975831014</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>287.3141106471616</v>
+        <v>287.3141106471617</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -13415,7 +13427,7 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901523</v>
+        <v>3803.886503901525</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
@@ -13427,22 +13439,22 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>5315.894937306298</v>
+        <v>5315.8949373063</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1256.376585107065</v>
+        <v>1256.376585107066</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5409.908834547959</v>
+        <v>5409.90883454796</v>
       </c>
     </row>
     <row r="95">
@@ -13473,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>407.3347841672957</v>
+        <v>407.3347841672958</v>
       </c>
       <c r="M95" s="131" t="n">
         <v>4423.797335108409</v>
@@ -13488,7 +13500,7 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665507</v>
+        <v>456.6186053665506</v>
       </c>
       <c r="S95" s="131" t="n">
         <v>4874.628103683081</v>
@@ -13604,10 +13616,10 @@
         <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>821.8541182771896</v>
+        <v>821.8541182771897</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>279.0679125332354</v>
+        <v>279.0679125332355</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>560.6457744410619</v>
@@ -13616,34 +13628,34 @@
         <v>7069.112073998887</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5816.280603427482</v>
+        <v>5816.280603427483</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.396351492128</v>
+        <v>901.3963514921277</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>300.6295457533571</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008076</v>
+        <v>571.6795744008077</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7589.986075073774</v>
+        <v>7589.986075073775</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.655996720889</v>
+        <v>6250.655996720888</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>987.1475980283611</v>
+        <v>987.1475980283614</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>321.7141332764122</v>
+        <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299143</v>
+        <v>593.5213632299141</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8153.039091255577</v>
+        <v>8153.039091255575</v>
       </c>
     </row>
     <row r="98">
@@ -13759,25 +13771,25 @@
         <v>151.8055148266722</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>6975.373307971806</v>
+        <v>6975.373307971811</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>10011.78106812466</v>
+        <v>10011.78106812467</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2639.658250704873</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>448.277386801492</v>
+        <v>448.2773868014629</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578742</v>
+        <v>7864.526914578741</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>11117.97029900591</v>
+        <v>11117.97029900588</v>
       </c>
     </row>
     <row r="100">
@@ -14010,40 +14022,40 @@
         <v>1135895.03984975</v>
       </c>
       <c r="K103" s="140" t="n">
-        <v>255058.7667674547</v>
+        <v>255058.7667674541</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58662.13438966972</v>
+        <v>58662.13438966971</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>4571.431810842299</v>
+        <v>4571.431810842301</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>1454187.372817716</v>
       </c>
       <c r="P103" s="139" t="n">
-        <v>1148419.705411591</v>
+        <v>1148419.705411597</v>
       </c>
       <c r="Q103" s="140" t="n">
-        <v>256655.8101514264</v>
+        <v>256655.8101514261</v>
       </c>
       <c r="R103" s="140" t="n">
-        <v>59175.12405820967</v>
+        <v>59175.12405820965</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>4844.630784977365</v>
+        <v>4844.630784977364</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>1469095.270406205</v>
+        <v>1469095.27040621</v>
       </c>
       <c r="V103" s="139" t="n">
-        <v>1159695.954534212</v>
+        <v>1159695.95453421</v>
       </c>
       <c r="W103" s="140" t="n">
-        <v>257981.4291505639</v>
+        <v>257981.4291505645</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>59655.70951589625</v>
+        <v>59655.70951589627</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>5336.818379074632</v>
@@ -14074,13 +14086,13 @@
         <v>48702</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1147367.644204108</v>
+        <v>1147367.644204109</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>257480.6278357828</v>
+        <v>257480.6278357822</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>59776.58186997884</v>
+        <v>59776.58186997882</v>
       </c>
       <c r="M104" s="143" t="n">
         <v>15819.80035996352</v>
@@ -14089,34 +14101,34 @@
         <v>1480444.654269833</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1160502.468979224</v>
+        <v>1160502.468979229</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>259202.0803003974</v>
+        <v>259202.0803003971</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>60373.31814510459</v>
+        <v>60373.31814510457</v>
       </c>
       <c r="S104" s="143" t="n">
         <v>17266.31177103306</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1497344.179195759</v>
+        <v>1497344.179195764</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1172449.016554634</v>
+        <v>1172449.016554633</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>260673.2307205008</v>
+        <v>260673.2307205013</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>60950.03499272167</v>
+        <v>60950.03499272169</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>19213.06972117535</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1513285.351989032</v>
+        <v>1513285.351989031</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -15149,7 +15161,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>45132914.73764992</v>
+        <v>45132914.73764993</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>57217.44053621583</v>
@@ -15745,7 +15757,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>6107506.857600685</v>
+        <v>6107506.857600686</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>817.0916674748539</v>
@@ -15899,10 +15911,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3672082.415149595</v>
+        <v>3672082.415149594</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>3491.467202798604</v>
+        <v>3491.467202798603</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -16133,7 +16145,7 @@
         <v>2576174.432302359</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>8051.17770688</v>
+        <v>8051.177706879999</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -16340,7 +16352,7 @@
         <v>2213943.575384721</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>397.0037510097247</v>
+        <v>397.0037510097246</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -16491,10 +16503,10 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1848416.173950569</v>
+        <v>1848416.173950568</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>3412.859287341888</v>
+        <v>3412.859287341889</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -16758,7 +16770,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>59180455.96349859</v>
+        <v>59180455.9634986</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>74258.41862736085</v>
@@ -16774,22 +16786,28 @@
       <c r="F51" s="12" t="n"/>
       <c r="G51" s="13" t="n"/>
       <c r="H51" s="14" t="n"/>
-      <c r="J51" s="11" t="n">
-        <v>2029</v>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
       </c>
       <c r="K51" s="12" t="n"/>
       <c r="L51" s="12" t="n"/>
       <c r="M51" s="13" t="n"/>
       <c r="N51" s="14" t="n"/>
-      <c r="P51" s="11" t="n">
-        <v>2028</v>
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
       </c>
       <c r="Q51" s="12" t="n"/>
       <c r="R51" s="12" t="n"/>
       <c r="S51" s="13" t="n"/>
       <c r="T51" s="14" t="n"/>
-      <c r="V51" s="11" t="n">
-        <v>2029</v>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
       </c>
       <c r="W51" s="12" t="n"/>
       <c r="X51" s="12" t="n"/>
@@ -16804,7 +16822,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>14682446.79018264</v>
+        <v>14682446.79018265</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>17288.14627740435</v>
@@ -17009,7 +17027,7 @@
         <v>11143727.90143079</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>12582.00236528829</v>
+        <v>12582.00236528828</v>
       </c>
     </row>
     <row r="54">
@@ -17370,13 +17388,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5043.97753572962</v>
+        <v>5043.977535729621</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>3672.153688237323</v>
+        <v>3672.153688237326</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1178.733620422441</v>
+        <v>1178.73362042244</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>276.6926051831596</v>
@@ -17385,7 +17403,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842924</v>
+        <v>5127.579913842926</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>3728.347202327301</v>
@@ -17400,7 +17418,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077948</v>
+        <v>5217.744981077949</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -17445,7 +17463,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
         <v>4111.798092690687</v>
@@ -17460,7 +17478,7 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.5777408532682</v>
+        <v>405.5777408532681</v>
       </c>
       <c r="S59" s="131" t="n">
         <v>4497.071348597412</v>
@@ -17604,10 +17622,10 @@
         <v>2710.474833260433</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.0358767901117</v>
+        <v>710.0358767901118</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>227.8577587891603</v>
+        <v>227.8577587891604</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>549.7124589894161</v>
@@ -17619,31 +17637,31 @@
         <v>2848.462218149934</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>760.0653829141094</v>
+        <v>760.0653829141091</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>237.7472517739969</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193557</v>
+        <v>560.6592858193558</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4406.934138657395</v>
+        <v>4406.934138657396</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>3005.608292870229</v>
+        <v>3005.608292870228</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.249027688854</v>
+        <v>816.2490276888542</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.3087850252182</v>
+        <v>582.308785025218</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4652.87302083473</v>
+        <v>4652.873020834729</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -17763,34 +17781,34 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862917</v>
+        <v>2315.01722486291</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>410.0571917407924</v>
+        <v>410.0571917407915</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.7306729614256</v>
+        <v>140.7306729614252</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>4860.049068810829</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375964</v>
+        <v>7725.854158375956</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303845</v>
+        <v>2462.596460303837</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224293</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>151.8055148266708</v>
+        <v>151.8055148266703</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>5497.21023131672</v>
+        <v>5497.210231316722</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.617991469664</v>
+        <v>8533.617991469659</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>2639.658250704611</v>
@@ -17802,10 +17820,10 @@
         <v>165.5077469208077</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865837</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292729</v>
+        <v>9544.249776292727</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17897,7 +17915,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>1080636.085854617</v>
+        <v>1080636.085854616</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>4715.065128560274</v>
@@ -18093,7 +18111,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>31870.3334309905</v>
+        <v>31870.33343099051</v>
       </c>
       <c r="K67" s="140" t="n">
         <v>4029.79567811647</v>
@@ -18102,16 +18120,16 @@
         <v>1407.005950657853</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>3375.286604353636</v>
+        <v>3375.286604353637</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>40682.42166411846</v>
+        <v>40682.42166411847</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>32493.07951996083</v>
+        <v>32493.07951996084</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>4092.276733052207</v>
+        <v>4092.276733052206</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>1367.292909233702</v>
@@ -18123,19 +18141,19 @@
         <v>41401.49046288215</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4402.675607700118</v>
+        <v>4402.67560770012</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>3796.051969460276</v>
+        <v>3796.051969460277</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -18189,10 +18207,10 @@
         <v>62122.69724342013</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665193</v>
+        <v>41476.29188665194</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>6453.081521411186</v>
+        <v>6453.081521411184</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>2439.116021870797</v>
@@ -18201,13 +18219,13 @@
         <v>14003.78216636889</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>64372.27159630281</v>
+        <v>64372.27159630282</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906604</v>
+        <v>43398.71923906603</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>6878.522835275836</v>
+        <v>6878.522835275839</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>2535.996836477477</v>
@@ -18216,7 +18234,7 @@
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.35109118339</v>
+        <v>68414.35109118337</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -18227,7 +18245,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>481256.0547738528</v>
+        <v>481256.0547738527</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>1895.838675356806</v>
@@ -18734,10 +18752,10 @@
         <v>183.3291939762258</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641998</v>
+        <v>131.7328156641999</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399727</v>
+        <v>44.13439203399725</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -18749,10 +18767,10 @@
         <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
-        <v>134.4005706694529</v>
+        <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.0557720216745</v>
+        <v>45.05577202167449</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -18761,7 +18779,7 @@
         <v>0</v>
       </c>
       <c r="Z76" s="132" t="n">
-        <v>192.1638534700123</v>
+        <v>192.1638534700124</v>
       </c>
     </row>
     <row r="77">
@@ -18792,7 +18810,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="131" t="n">
-        <v>46.76991949101995</v>
+        <v>46.76991949101996</v>
       </c>
       <c r="M77" s="131" t="n">
         <v>311.9992424177221</v>
@@ -18807,13 +18825,13 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.04086451328254</v>
+        <v>51.04086451328255</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>377.5567550856683</v>
+        <v>377.5567550856682</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>428.5976195989509</v>
+        <v>428.5976195989508</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -18822,13 +18840,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91560864239314</v>
+        <v>55.91560864239312</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>486.2580302793615</v>
+        <v>486.2580302793614</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>542.1736389217547</v>
+        <v>542.1736389217546</v>
       </c>
     </row>
     <row r="78">
@@ -18938,10 +18956,10 @@
         <v>2967.818385277548</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780187</v>
+        <v>141.3309685780186</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88229397936017</v>
+        <v>62.88229397936021</v>
       </c>
       <c r="S79" s="131" t="n">
         <v>11.02028858145198</v>
@@ -18956,7 +18974,7 @@
         <v>170.8985703395071</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.00721802598373</v>
+        <v>73.00721802598372</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>11.21257820469615</v>
@@ -19078,10 +19096,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>1478.163076655088</v>
+        <v>1478.163076655087</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>1478.163076655088</v>
+        <v>1478.163076655087</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>0</v>
@@ -19326,49 +19344,49 @@
         <v>0</v>
       </c>
       <c r="J85" s="139" t="n">
-        <v>1104024.706418759</v>
+        <v>1104024.70641876</v>
       </c>
       <c r="K85" s="140" t="n">
-        <v>251028.9710893382</v>
+        <v>251028.9710893376</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57255.12843901187</v>
+        <v>57255.12843901185</v>
       </c>
       <c r="M85" s="140" t="n">
-        <v>1196.145206488663</v>
+        <v>1196.145206488664</v>
       </c>
       <c r="N85" s="141" t="n">
         <v>1413504.951153598</v>
       </c>
       <c r="P85" s="139" t="n">
-        <v>1115926.625891631</v>
+        <v>1115926.625891636</v>
       </c>
       <c r="Q85" s="140" t="n">
-        <v>252563.5334183742</v>
+        <v>252563.5334183738</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>57807.83114897597</v>
+        <v>57807.83114897595</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1395.789484341962</v>
+        <v>1395.789484341961</v>
       </c>
       <c r="T85" s="141" t="n">
-        <v>1427693.779943323</v>
+        <v>1427693.779943328</v>
       </c>
       <c r="V85" s="139" t="n">
-        <v>1125670.849041048</v>
+        <v>1125670.849041047</v>
       </c>
       <c r="W85" s="140" t="n">
-        <v>253578.7535428638</v>
+        <v>253578.7535428643</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>58272.40781879693</v>
+        <v>58272.40781879695</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>1540.766409614355</v>
       </c>
       <c r="Z85" s="141" t="n">
-        <v>1439062.776812323</v>
+        <v>1439062.776812322</v>
       </c>
     </row>
     <row r="86" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -19393,13 +19411,13 @@
         <v>3478</v>
       </c>
       <c r="J86" s="142" t="n">
-        <v>1106850.058062584</v>
+        <v>1106850.058062585</v>
       </c>
       <c r="K86" s="143" t="n">
-        <v>251183.7261189914</v>
+        <v>251183.7261189908</v>
       </c>
       <c r="L86" s="143" t="n">
-        <v>57365.21870971905</v>
+        <v>57365.21870971904</v>
       </c>
       <c r="M86" s="143" t="n">
         <v>2922.954135118953</v>
@@ -19408,31 +19426,31 @@
         <v>1418321.957026413</v>
       </c>
       <c r="P86" s="142" t="n">
-        <v>1119026.177092572</v>
+        <v>1119026.177092578</v>
       </c>
       <c r="Q86" s="143" t="n">
-        <v>252748.9987789862</v>
+        <v>252748.9987789859</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>57934.20212323379</v>
+        <v>57934.20212323377</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>3262.52960466417</v>
+        <v>3262.529604664169</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>1432971.907599456</v>
+        <v>1432971.907599461</v>
       </c>
       <c r="V86" s="142" t="n">
-        <v>1129050.297315568</v>
+        <v>1129050.297315567</v>
       </c>
       <c r="W86" s="143" t="n">
-        <v>253794.707885225</v>
+        <v>253794.7078852255</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58414.03815624419</v>
+        <v>58414.03815624421</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>3611.957540811319</v>
+        <v>3611.957540811318</v>
       </c>
       <c r="Z86" s="144" t="n">
         <v>1444871.000897848</v>
@@ -19930,7 +19948,7 @@
         <v>1189.94975831014</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>287.3141106471616</v>
+        <v>287.3141106471617</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -19939,7 +19957,7 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901523</v>
+        <v>3803.886503901525</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
@@ -19951,22 +19969,22 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>5315.894937306298</v>
+        <v>5315.8949373063</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1256.376585107065</v>
+        <v>1256.376585107066</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5409.908834547959</v>
+        <v>5409.90883454796</v>
       </c>
     </row>
     <row r="95">
@@ -19997,7 +20015,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>407.3347841672957</v>
+        <v>407.3347841672958</v>
       </c>
       <c r="M95" s="131" t="n">
         <v>4423.797335108409</v>
@@ -20012,7 +20030,7 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665507</v>
+        <v>456.6186053665506</v>
       </c>
       <c r="S95" s="131" t="n">
         <v>4874.628103683081</v>
@@ -20128,10 +20146,10 @@
         <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>821.8541182771896</v>
+        <v>821.8541182771897</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>279.0679125332354</v>
+        <v>279.0679125332355</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>560.6457744410619</v>
@@ -20140,34 +20158,34 @@
         <v>7069.112073998887</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5816.280603427482</v>
+        <v>5816.280603427483</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.396351492128</v>
+        <v>901.3963514921277</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>300.6295457533571</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008076</v>
+        <v>571.6795744008077</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7589.986075073774</v>
+        <v>7589.986075073775</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.655996720889</v>
+        <v>6250.655996720888</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>987.1475980283611</v>
+        <v>987.1475980283614</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>321.7141332764122</v>
+        <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299143</v>
+        <v>593.5213632299141</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8153.039091255577</v>
+        <v>8153.039091255575</v>
       </c>
     </row>
     <row r="98">
@@ -20283,25 +20301,25 @@
         <v>151.8055148266722</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>6975.373307971806</v>
+        <v>6975.373307971811</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>10011.78106812466</v>
+        <v>10011.78106812467</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2639.658250704873</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>448.277386801492</v>
+        <v>448.2773868014629</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578742</v>
+        <v>7864.526914578741</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>11117.97029900591</v>
+        <v>11117.97029900588</v>
       </c>
     </row>
     <row r="100">
@@ -20534,40 +20552,40 @@
         <v>1135895.03984975</v>
       </c>
       <c r="K103" s="140" t="n">
-        <v>255058.7667674547</v>
+        <v>255058.7667674541</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58662.13438966972</v>
+        <v>58662.13438966971</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>4571.431810842299</v>
+        <v>4571.431810842301</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>1454187.372817716</v>
       </c>
       <c r="P103" s="139" t="n">
-        <v>1148419.705411591</v>
+        <v>1148419.705411597</v>
       </c>
       <c r="Q103" s="140" t="n">
-        <v>256655.8101514264</v>
+        <v>256655.8101514261</v>
       </c>
       <c r="R103" s="140" t="n">
-        <v>59175.12405820967</v>
+        <v>59175.12405820965</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>4844.630784977365</v>
+        <v>4844.630784977364</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>1469095.270406205</v>
+        <v>1469095.27040621</v>
       </c>
       <c r="V103" s="139" t="n">
-        <v>1159695.954534212</v>
+        <v>1159695.95453421</v>
       </c>
       <c r="W103" s="140" t="n">
-        <v>257981.4291505639</v>
+        <v>257981.4291505645</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>59655.70951589625</v>
+        <v>59655.70951589627</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>5336.818379074632</v>
@@ -20598,13 +20616,13 @@
         <v>48702</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1147367.644204108</v>
+        <v>1147367.644204109</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>257480.6278357828</v>
+        <v>257480.6278357822</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>59776.58186997884</v>
+        <v>59776.58186997882</v>
       </c>
       <c r="M104" s="143" t="n">
         <v>15819.80035996352</v>
@@ -20613,34 +20631,34 @@
         <v>1480444.654269833</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1160502.468979224</v>
+        <v>1160502.468979229</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>259202.0803003974</v>
+        <v>259202.0803003971</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>60373.31814510459</v>
+        <v>60373.31814510457</v>
       </c>
       <c r="S104" s="143" t="n">
         <v>17266.31177103306</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1497344.179195759</v>
+        <v>1497344.179195764</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1172449.016554634</v>
+        <v>1172449.016554633</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>260673.2307205008</v>
+        <v>260673.2307205013</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>60950.03499272167</v>
+        <v>60950.03499272169</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>19213.06972117535</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1513285.351989032</v>
+        <v>1513285.351989031</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -21673,7 +21691,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>55511534.03972473</v>
+        <v>55511534.03972472</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>68660.92484379245</v>
@@ -21981,10 +21999,10 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>13133392.16558732</v>
+        <v>13133392.16558731</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>6257.992427689866</v>
+        <v>6257.992427689867</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -22124,7 +22142,7 @@
         <v>11081682.71547412</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>13115.78537471265</v>
+        <v>13115.78537471264</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -22423,10 +22441,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>4106020.770573939</v>
+        <v>4106020.770573941</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>3734.68760967116</v>
+        <v>3734.687609671161</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -22654,7 +22672,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>3031073.90433326</v>
+        <v>3031073.904333259</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>5996.680645260307</v>
@@ -23269,7 +23287,7 @@
         <v>78440635.8474838</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>8338.628013770054</v>
+        <v>8338.628013770052</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -23298,22 +23316,28 @@
       <c r="F51" s="12" t="n"/>
       <c r="G51" s="13" t="n"/>
       <c r="H51" s="14" t="n"/>
-      <c r="J51" s="11" t="n">
-        <v>2030</v>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
       </c>
       <c r="K51" s="12" t="n"/>
       <c r="L51" s="12" t="n"/>
       <c r="M51" s="13" t="n"/>
       <c r="N51" s="14" t="n"/>
-      <c r="P51" s="11" t="n">
-        <v>2028</v>
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
       </c>
       <c r="Q51" s="12" t="n"/>
       <c r="R51" s="12" t="n"/>
       <c r="S51" s="13" t="n"/>
       <c r="T51" s="14" t="n"/>
-      <c r="V51" s="11" t="n">
-        <v>2029</v>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
       </c>
       <c r="W51" s="12" t="n"/>
       <c r="X51" s="12" t="n"/>
@@ -23611,7 +23635,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>9775955.076188011</v>
+        <v>9775955.076188013</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>23659.13977320257</v>
@@ -23773,7 +23797,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>3993342.162518921</v>
+        <v>3993342.16251892</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>12535.421478272</v>
@@ -23854,7 +23878,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>3186124.42376193</v>
+        <v>3186124.423761929</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>251.5675531601408</v>
@@ -23894,13 +23918,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5043.97753572962</v>
+        <v>5043.977535729621</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>3672.153688237323</v>
+        <v>3672.153688237326</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1178.733620422441</v>
+        <v>1178.73362042244</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>276.6926051831596</v>
@@ -23909,7 +23933,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842924</v>
+        <v>5127.579913842926</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>3728.347202327301</v>
@@ -23924,7 +23948,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077948</v>
+        <v>5217.744981077949</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -23969,7 +23993,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
         <v>4111.798092690687</v>
@@ -23984,7 +24008,7 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.5777408532682</v>
+        <v>405.5777408532681</v>
       </c>
       <c r="S59" s="131" t="n">
         <v>4497.071348597412</v>
@@ -24128,10 +24152,10 @@
         <v>2710.474833260433</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.0358767901117</v>
+        <v>710.0358767901118</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>227.8577587891603</v>
+        <v>227.8577587891604</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>549.7124589894161</v>
@@ -24143,31 +24167,31 @@
         <v>2848.462218149934</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>760.0653829141094</v>
+        <v>760.0653829141091</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>237.7472517739969</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193557</v>
+        <v>560.6592858193558</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4406.934138657395</v>
+        <v>4406.934138657396</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>3005.608292870229</v>
+        <v>3005.608292870228</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.249027688854</v>
+        <v>816.2490276888542</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.3087850252182</v>
+        <v>582.308785025218</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4652.87302083473</v>
+        <v>4652.873020834729</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -24287,34 +24311,34 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862917</v>
+        <v>2315.01722486291</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>410.0571917407924</v>
+        <v>410.0571917407915</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.7306729614256</v>
+        <v>140.7306729614252</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>4860.049068810829</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375964</v>
+        <v>7725.854158375956</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303845</v>
+        <v>2462.596460303837</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224293</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>151.8055148266708</v>
+        <v>151.8055148266703</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>5497.21023131672</v>
+        <v>5497.210231316722</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.617991469664</v>
+        <v>8533.617991469659</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>2639.658250704611</v>
@@ -24326,10 +24350,10 @@
         <v>165.5077469208077</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865837</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292729</v>
+        <v>9544.249776292727</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24343,7 +24367,7 @@
         <v>1196600.967496471</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>217.5932425827678</v>
+        <v>217.5932425827679</v>
       </c>
     </row>
     <row r="64">
@@ -24510,7 +24534,7 @@
         <v>898764.3735085729</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>539.0692909435293</v>
+        <v>539.0692909435292</v>
       </c>
     </row>
     <row r="66">
@@ -24589,7 +24613,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>795311.5989671435</v>
+        <v>795311.5989671433</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>2348.723611867773</v>
@@ -24617,7 +24641,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>31870.3334309905</v>
+        <v>31870.33343099051</v>
       </c>
       <c r="K67" s="140" t="n">
         <v>4029.79567811647</v>
@@ -24626,16 +24650,16 @@
         <v>1407.005950657853</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>3375.286604353636</v>
+        <v>3375.286604353637</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>40682.42166411846</v>
+        <v>40682.42166411847</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>32493.07951996083</v>
+        <v>32493.07951996084</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>4092.276733052207</v>
+        <v>4092.276733052206</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>1367.292909233702</v>
@@ -24647,19 +24671,19 @@
         <v>41401.49046288215</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4402.675607700118</v>
+        <v>4402.67560770012</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>3796.051969460276</v>
+        <v>3796.051969460277</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -24670,10 +24694,10 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>586259.3862819772</v>
+        <v>586259.3862819769</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>539.185129658912</v>
+        <v>539.1851296589119</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -24713,10 +24737,10 @@
         <v>62122.69724342013</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665193</v>
+        <v>41476.29188665194</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>6453.081521411186</v>
+        <v>6453.081521411184</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>2439.116021870797</v>
@@ -24725,13 +24749,13 @@
         <v>14003.78216636889</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>64372.27159630281</v>
+        <v>64372.27159630282</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906604</v>
+        <v>43398.71923906603</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>6878.522835275836</v>
+        <v>6878.522835275839</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>2535.996836477477</v>
@@ -24740,7 +24764,7 @@
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.35109118339</v>
+        <v>68414.35109118337</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -25258,10 +25282,10 @@
         <v>183.3291939762258</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641998</v>
+        <v>131.7328156641999</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399727</v>
+        <v>44.13439203399725</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -25273,10 +25297,10 @@
         <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
-        <v>134.4005706694529</v>
+        <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.0557720216745</v>
+        <v>45.05577202167449</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -25285,7 +25309,7 @@
         <v>0</v>
       </c>
       <c r="Z76" s="132" t="n">
-        <v>192.1638534700123</v>
+        <v>192.1638534700124</v>
       </c>
     </row>
     <row r="77">
@@ -25316,7 +25340,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="131" t="n">
-        <v>46.76991949101995</v>
+        <v>46.76991949101996</v>
       </c>
       <c r="M77" s="131" t="n">
         <v>311.9992424177221</v>
@@ -25331,13 +25355,13 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.04086451328254</v>
+        <v>51.04086451328255</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>377.5567550856683</v>
+        <v>377.5567550856682</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>428.5976195989509</v>
+        <v>428.5976195989508</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -25346,13 +25370,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91560864239314</v>
+        <v>55.91560864239312</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>486.2580302793615</v>
+        <v>486.2580302793614</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>542.1736389217547</v>
+        <v>542.1736389217546</v>
       </c>
     </row>
     <row r="78">
@@ -25462,10 +25486,10 @@
         <v>2967.818385277548</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780187</v>
+        <v>141.3309685780186</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88229397936017</v>
+        <v>62.88229397936021</v>
       </c>
       <c r="S79" s="131" t="n">
         <v>11.02028858145198</v>
@@ -25480,7 +25504,7 @@
         <v>170.8985703395071</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.00721802598373</v>
+        <v>73.00721802598372</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>11.21257820469615</v>
@@ -25602,10 +25626,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>1478.163076655088</v>
+        <v>1478.163076655087</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>1478.163076655088</v>
+        <v>1478.163076655087</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>0</v>
@@ -25850,49 +25874,49 @@
         <v>0</v>
       </c>
       <c r="J85" s="139" t="n">
-        <v>1104024.706418759</v>
+        <v>1104024.70641876</v>
       </c>
       <c r="K85" s="140" t="n">
-        <v>251028.9710893382</v>
+        <v>251028.9710893376</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57255.12843901187</v>
+        <v>57255.12843901185</v>
       </c>
       <c r="M85" s="140" t="n">
-        <v>1196.145206488663</v>
+        <v>1196.145206488664</v>
       </c>
       <c r="N85" s="141" t="n">
         <v>1413504.951153598</v>
       </c>
       <c r="P85" s="139" t="n">
-        <v>1115926.625891631</v>
+        <v>1115926.625891636</v>
       </c>
       <c r="Q85" s="140" t="n">
-        <v>252563.5334183742</v>
+        <v>252563.5334183738</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>57807.83114897597</v>
+        <v>57807.83114897595</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1395.789484341962</v>
+        <v>1395.789484341961</v>
       </c>
       <c r="T85" s="141" t="n">
-        <v>1427693.779943323</v>
+        <v>1427693.779943328</v>
       </c>
       <c r="V85" s="139" t="n">
-        <v>1125670.849041048</v>
+        <v>1125670.849041047</v>
       </c>
       <c r="W85" s="140" t="n">
-        <v>253578.7535428638</v>
+        <v>253578.7535428643</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>58272.40781879693</v>
+        <v>58272.40781879695</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>1540.766409614355</v>
       </c>
       <c r="Z85" s="141" t="n">
-        <v>1439062.776812323</v>
+        <v>1439062.776812322</v>
       </c>
     </row>
     <row r="86" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -25917,13 +25941,13 @@
         <v>3478</v>
       </c>
       <c r="J86" s="142" t="n">
-        <v>1106850.058062584</v>
+        <v>1106850.058062585</v>
       </c>
       <c r="K86" s="143" t="n">
-        <v>251183.7261189914</v>
+        <v>251183.7261189908</v>
       </c>
       <c r="L86" s="143" t="n">
-        <v>57365.21870971905</v>
+        <v>57365.21870971904</v>
       </c>
       <c r="M86" s="143" t="n">
         <v>2922.954135118953</v>
@@ -25932,31 +25956,31 @@
         <v>1418321.957026413</v>
       </c>
       <c r="P86" s="142" t="n">
-        <v>1119026.177092572</v>
+        <v>1119026.177092578</v>
       </c>
       <c r="Q86" s="143" t="n">
-        <v>252748.9987789862</v>
+        <v>252748.9987789859</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>57934.20212323379</v>
+        <v>57934.20212323377</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>3262.52960466417</v>
+        <v>3262.529604664169</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>1432971.907599456</v>
+        <v>1432971.907599461</v>
       </c>
       <c r="V86" s="142" t="n">
-        <v>1129050.297315568</v>
+        <v>1129050.297315567</v>
       </c>
       <c r="W86" s="143" t="n">
-        <v>253794.707885225</v>
+        <v>253794.7078852255</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58414.03815624419</v>
+        <v>58414.03815624421</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>3611.957540811319</v>
+        <v>3611.957540811318</v>
       </c>
       <c r="Z86" s="144" t="n">
         <v>1444871.000897848</v>
@@ -26454,7 +26478,7 @@
         <v>1189.94975831014</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>287.3141106471616</v>
+        <v>287.3141106471617</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -26463,7 +26487,7 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901523</v>
+        <v>3803.886503901525</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
@@ -26475,22 +26499,22 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>5315.894937306298</v>
+        <v>5315.8949373063</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1256.376585107065</v>
+        <v>1256.376585107066</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5409.908834547959</v>
+        <v>5409.90883454796</v>
       </c>
     </row>
     <row r="95">
@@ -26521,7 +26545,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>407.3347841672957</v>
+        <v>407.3347841672958</v>
       </c>
       <c r="M95" s="131" t="n">
         <v>4423.797335108409</v>
@@ -26536,7 +26560,7 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665507</v>
+        <v>456.6186053665506</v>
       </c>
       <c r="S95" s="131" t="n">
         <v>4874.628103683081</v>
@@ -26652,10 +26676,10 @@
         <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>821.8541182771896</v>
+        <v>821.8541182771897</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>279.0679125332354</v>
+        <v>279.0679125332355</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>560.6457744410619</v>
@@ -26664,34 +26688,34 @@
         <v>7069.112073998887</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5816.280603427482</v>
+        <v>5816.280603427483</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.396351492128</v>
+        <v>901.3963514921277</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>300.6295457533571</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008076</v>
+        <v>571.6795744008077</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7589.986075073774</v>
+        <v>7589.986075073775</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.655996720889</v>
+        <v>6250.655996720888</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>987.1475980283611</v>
+        <v>987.1475980283614</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>321.7141332764122</v>
+        <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299143</v>
+        <v>593.5213632299141</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8153.039091255577</v>
+        <v>8153.039091255575</v>
       </c>
     </row>
     <row r="98">
@@ -26807,25 +26831,25 @@
         <v>151.8055148266722</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>6975.373307971806</v>
+        <v>6975.373307971811</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>10011.78106812466</v>
+        <v>10011.78106812467</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2639.658250704873</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>448.277386801492</v>
+        <v>448.2773868014629</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578742</v>
+        <v>7864.526914578741</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>11117.97029900591</v>
+        <v>11117.97029900588</v>
       </c>
     </row>
     <row r="100">
@@ -27058,40 +27082,40 @@
         <v>1135895.03984975</v>
       </c>
       <c r="K103" s="140" t="n">
-        <v>255058.7667674547</v>
+        <v>255058.7667674541</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58662.13438966972</v>
+        <v>58662.13438966971</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>4571.431810842299</v>
+        <v>4571.431810842301</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>1454187.372817716</v>
       </c>
       <c r="P103" s="139" t="n">
-        <v>1148419.705411591</v>
+        <v>1148419.705411597</v>
       </c>
       <c r="Q103" s="140" t="n">
-        <v>256655.8101514264</v>
+        <v>256655.8101514261</v>
       </c>
       <c r="R103" s="140" t="n">
-        <v>59175.12405820967</v>
+        <v>59175.12405820965</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>4844.630784977365</v>
+        <v>4844.630784977364</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>1469095.270406205</v>
+        <v>1469095.27040621</v>
       </c>
       <c r="V103" s="139" t="n">
-        <v>1159695.954534212</v>
+        <v>1159695.95453421</v>
       </c>
       <c r="W103" s="140" t="n">
-        <v>257981.4291505639</v>
+        <v>257981.4291505645</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>59655.70951589625</v>
+        <v>59655.70951589627</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>5336.818379074632</v>
@@ -27122,13 +27146,13 @@
         <v>48702</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1147367.644204108</v>
+        <v>1147367.644204109</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>257480.6278357828</v>
+        <v>257480.6278357822</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>59776.58186997884</v>
+        <v>59776.58186997882</v>
       </c>
       <c r="M104" s="143" t="n">
         <v>15819.80035996352</v>
@@ -27137,34 +27161,34 @@
         <v>1480444.654269833</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1160502.468979224</v>
+        <v>1160502.468979229</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>259202.0803003974</v>
+        <v>259202.0803003971</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>60373.31814510459</v>
+        <v>60373.31814510457</v>
       </c>
       <c r="S104" s="143" t="n">
         <v>17266.31177103306</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1497344.179195759</v>
+        <v>1497344.179195764</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1172449.016554634</v>
+        <v>1172449.016554633</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>260673.2307205008</v>
+        <v>260673.2307205013</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>60950.03499272167</v>
+        <v>60950.03499272169</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>19213.06972117535</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1513285.351989032</v>
+        <v>1513285.351989031</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -28197,7 +28221,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>68972449.84517561</v>
+        <v>68972449.84517562</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>82393.10616487112</v>
@@ -28277,7 +28301,7 @@
         <v>31207641.60542405</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>2045.210599589361</v>
+        <v>2045.210599589362</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -28505,10 +28529,10 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>16778205.04829702</v>
+        <v>16778205.04829703</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>7591.883513651963</v>
+        <v>7591.883513651962</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -28648,7 +28672,7 @@
         <v>11390859.83017859</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>529.9779303762053</v>
+        <v>529.9779303762052</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -28793,7 +28817,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>7160083.484604075</v>
+        <v>7160083.484604074</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>850.3564973906491</v>
@@ -28870,7 +28894,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>6644196.688008283</v>
+        <v>6644196.688008282</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>11760.22606198546</v>
@@ -28947,10 +28971,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>5250497.495615019</v>
+        <v>5250497.495615018</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>15780.3083054848</v>
+        <v>15780.30830548479</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -29024,7 +29048,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>4630598.152264988</v>
+        <v>4630598.152264991</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>3987.994031430143</v>
@@ -29404,7 +29428,7 @@
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>418.9450962243397</v>
+        <v>418.9450962243398</v>
       </c>
     </row>
     <row r="42">
@@ -29619,7 +29643,7 @@
         <v>2250731.006220551</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>2957.226786839573</v>
+        <v>2957.226786839575</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -29822,22 +29846,28 @@
       <c r="F51" s="12" t="n"/>
       <c r="G51" s="13" t="n"/>
       <c r="H51" s="14" t="n"/>
-      <c r="J51" s="11" t="n">
-        <v>2031</v>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
       </c>
       <c r="K51" s="12" t="n"/>
       <c r="L51" s="12" t="n"/>
       <c r="M51" s="13" t="n"/>
       <c r="N51" s="14" t="n"/>
-      <c r="P51" s="11" t="n">
-        <v>2028</v>
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
       </c>
       <c r="Q51" s="12" t="n"/>
       <c r="R51" s="12" t="n"/>
       <c r="S51" s="13" t="n"/>
       <c r="T51" s="14" t="n"/>
-      <c r="V51" s="11" t="n">
-        <v>2029</v>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
       </c>
       <c r="W51" s="12" t="n"/>
       <c r="X51" s="12" t="n"/>
@@ -29973,7 +30003,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>18930527.69219387</v>
+        <v>18930527.69219388</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>8258.907574637857</v>
@@ -30297,10 +30327,10 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>3711330.712964057</v>
+        <v>3711330.712964056</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>251.6271412030643</v>
+        <v>251.6271412030642</v>
       </c>
     </row>
     <row r="57">
@@ -30418,13 +30448,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5043.97753572962</v>
+        <v>5043.977535729621</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>3672.153688237323</v>
+        <v>3672.153688237326</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1178.733620422441</v>
+        <v>1178.73362042244</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>276.6926051831596</v>
@@ -30433,7 +30463,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842924</v>
+        <v>5127.579913842926</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>3728.347202327301</v>
@@ -30448,7 +30478,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077948</v>
+        <v>5217.744981077949</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -30493,7 +30523,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
         <v>4111.798092690687</v>
@@ -30508,7 +30538,7 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.5777408532682</v>
+        <v>405.5777408532681</v>
       </c>
       <c r="S59" s="131" t="n">
         <v>4497.071348597412</v>
@@ -30652,10 +30682,10 @@
         <v>2710.474833260433</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.0358767901117</v>
+        <v>710.0358767901118</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>227.8577587891603</v>
+        <v>227.8577587891604</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>549.7124589894161</v>
@@ -30667,31 +30697,31 @@
         <v>2848.462218149934</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>760.0653829141094</v>
+        <v>760.0653829141091</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>237.7472517739969</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193557</v>
+        <v>560.6592858193558</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4406.934138657395</v>
+        <v>4406.934138657396</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>3005.608292870229</v>
+        <v>3005.608292870228</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.249027688854</v>
+        <v>816.2490276888542</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.3087850252182</v>
+        <v>582.308785025218</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4652.87302083473</v>
+        <v>4652.873020834729</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -30702,7 +30732,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1641076.747338311</v>
+        <v>1641076.74733831</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>3969.264717832511</v>
@@ -30811,34 +30841,34 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862917</v>
+        <v>2315.01722486291</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>410.0571917407924</v>
+        <v>410.0571917407915</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.7306729614256</v>
+        <v>140.7306729614252</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>4860.049068810829</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375964</v>
+        <v>7725.854158375956</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303845</v>
+        <v>2462.596460303837</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224293</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>151.8055148266708</v>
+        <v>151.8055148266703</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>5497.21023131672</v>
+        <v>5497.210231316722</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.617991469664</v>
+        <v>8533.617991469659</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>2639.658250704611</v>
@@ -30850,10 +30880,10 @@
         <v>165.5077469208077</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865837</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292729</v>
+        <v>9544.249776292727</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -31034,7 +31064,7 @@
         <v>978899.2254386998</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>554.0823706963065</v>
+        <v>554.0823706963064</v>
       </c>
     </row>
     <row r="66">
@@ -31141,7 +31171,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>31870.3334309905</v>
+        <v>31870.33343099051</v>
       </c>
       <c r="K67" s="140" t="n">
         <v>4029.79567811647</v>
@@ -31150,16 +31180,16 @@
         <v>1407.005950657853</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>3375.286604353636</v>
+        <v>3375.286604353637</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>40682.42166411846</v>
+        <v>40682.42166411847</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>32493.07951996083</v>
+        <v>32493.07951996084</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>4092.276733052207</v>
+        <v>4092.276733052206</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>1367.292909233702</v>
@@ -31171,19 +31201,19 @@
         <v>41401.49046288215</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4402.675607700118</v>
+        <v>4402.67560770012</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>3796.051969460276</v>
+        <v>3796.051969460277</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -31197,7 +31227,7 @@
         <v>735104.4081649769</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>636.2384529975161</v>
+        <v>636.2384529975162</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -31237,10 +31267,10 @@
         <v>62122.69724342013</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665193</v>
+        <v>41476.29188665194</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>6453.081521411186</v>
+        <v>6453.081521411184</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>2439.116021870797</v>
@@ -31249,13 +31279,13 @@
         <v>14003.78216636889</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>64372.27159630281</v>
+        <v>64372.27159630282</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906604</v>
+        <v>43398.71923906603</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>6878.522835275836</v>
+        <v>6878.522835275839</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>2535.996836477477</v>
@@ -31264,7 +31294,7 @@
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.35109118339</v>
+        <v>68414.35109118337</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -31782,10 +31812,10 @@
         <v>183.3291939762258</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641998</v>
+        <v>131.7328156641999</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399727</v>
+        <v>44.13439203399725</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -31797,10 +31827,10 @@
         <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
-        <v>134.4005706694529</v>
+        <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.0557720216745</v>
+        <v>45.05577202167449</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -31809,7 +31839,7 @@
         <v>0</v>
       </c>
       <c r="Z76" s="132" t="n">
-        <v>192.1638534700123</v>
+        <v>192.1638534700124</v>
       </c>
     </row>
     <row r="77">
@@ -31840,7 +31870,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="131" t="n">
-        <v>46.76991949101995</v>
+        <v>46.76991949101996</v>
       </c>
       <c r="M77" s="131" t="n">
         <v>311.9992424177221</v>
@@ -31855,13 +31885,13 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.04086451328254</v>
+        <v>51.04086451328255</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>377.5567550856683</v>
+        <v>377.5567550856682</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>428.5976195989509</v>
+        <v>428.5976195989508</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -31870,13 +31900,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91560864239314</v>
+        <v>55.91560864239312</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>486.2580302793615</v>
+        <v>486.2580302793614</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>542.1736389217547</v>
+        <v>542.1736389217546</v>
       </c>
     </row>
     <row r="78">
@@ -31986,10 +32016,10 @@
         <v>2967.818385277548</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780187</v>
+        <v>141.3309685780186</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88229397936017</v>
+        <v>62.88229397936021</v>
       </c>
       <c r="S79" s="131" t="n">
         <v>11.02028858145198</v>
@@ -32004,7 +32034,7 @@
         <v>170.8985703395071</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.00721802598373</v>
+        <v>73.00721802598372</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>11.21257820469615</v>
@@ -32126,10 +32156,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>1478.163076655088</v>
+        <v>1478.163076655087</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>1478.163076655088</v>
+        <v>1478.163076655087</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>0</v>
@@ -32374,49 +32404,49 @@
         <v>0</v>
       </c>
       <c r="J85" s="139" t="n">
-        <v>1104024.706418759</v>
+        <v>1104024.70641876</v>
       </c>
       <c r="K85" s="140" t="n">
-        <v>251028.9710893382</v>
+        <v>251028.9710893376</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57255.12843901187</v>
+        <v>57255.12843901185</v>
       </c>
       <c r="M85" s="140" t="n">
-        <v>1196.145206488663</v>
+        <v>1196.145206488664</v>
       </c>
       <c r="N85" s="141" t="n">
         <v>1413504.951153598</v>
       </c>
       <c r="P85" s="139" t="n">
-        <v>1115926.625891631</v>
+        <v>1115926.625891636</v>
       </c>
       <c r="Q85" s="140" t="n">
-        <v>252563.5334183742</v>
+        <v>252563.5334183738</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>57807.83114897597</v>
+        <v>57807.83114897595</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1395.789484341962</v>
+        <v>1395.789484341961</v>
       </c>
       <c r="T85" s="141" t="n">
-        <v>1427693.779943323</v>
+        <v>1427693.779943328</v>
       </c>
       <c r="V85" s="139" t="n">
-        <v>1125670.849041048</v>
+        <v>1125670.849041047</v>
       </c>
       <c r="W85" s="140" t="n">
-        <v>253578.7535428638</v>
+        <v>253578.7535428643</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>58272.40781879693</v>
+        <v>58272.40781879695</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>1540.766409614355</v>
       </c>
       <c r="Z85" s="141" t="n">
-        <v>1439062.776812323</v>
+        <v>1439062.776812322</v>
       </c>
     </row>
     <row r="86" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -32441,13 +32471,13 @@
         <v>3478</v>
       </c>
       <c r="J86" s="142" t="n">
-        <v>1106850.058062584</v>
+        <v>1106850.058062585</v>
       </c>
       <c r="K86" s="143" t="n">
-        <v>251183.7261189914</v>
+        <v>251183.7261189908</v>
       </c>
       <c r="L86" s="143" t="n">
-        <v>57365.21870971905</v>
+        <v>57365.21870971904</v>
       </c>
       <c r="M86" s="143" t="n">
         <v>2922.954135118953</v>
@@ -32456,31 +32486,31 @@
         <v>1418321.957026413</v>
       </c>
       <c r="P86" s="142" t="n">
-        <v>1119026.177092572</v>
+        <v>1119026.177092578</v>
       </c>
       <c r="Q86" s="143" t="n">
-        <v>252748.9987789862</v>
+        <v>252748.9987789859</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>57934.20212323379</v>
+        <v>57934.20212323377</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>3262.52960466417</v>
+        <v>3262.529604664169</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>1432971.907599456</v>
+        <v>1432971.907599461</v>
       </c>
       <c r="V86" s="142" t="n">
-        <v>1129050.297315568</v>
+        <v>1129050.297315567</v>
       </c>
       <c r="W86" s="143" t="n">
-        <v>253794.707885225</v>
+        <v>253794.7078852255</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58414.03815624419</v>
+        <v>58414.03815624421</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>3611.957540811319</v>
+        <v>3611.957540811318</v>
       </c>
       <c r="Z86" s="144" t="n">
         <v>1444871.000897848</v>
@@ -32978,7 +33008,7 @@
         <v>1189.94975831014</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>287.3141106471616</v>
+        <v>287.3141106471617</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -32987,7 +33017,7 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901523</v>
+        <v>3803.886503901525</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
@@ -32999,22 +33029,22 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>5315.894937306298</v>
+        <v>5315.8949373063</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1256.376585107065</v>
+        <v>1256.376585107066</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5409.908834547959</v>
+        <v>5409.90883454796</v>
       </c>
     </row>
     <row r="95">
@@ -33045,7 +33075,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>407.3347841672957</v>
+        <v>407.3347841672958</v>
       </c>
       <c r="M95" s="131" t="n">
         <v>4423.797335108409</v>
@@ -33060,7 +33090,7 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665507</v>
+        <v>456.6186053665506</v>
       </c>
       <c r="S95" s="131" t="n">
         <v>4874.628103683081</v>
@@ -33176,10 +33206,10 @@
         <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>821.8541182771896</v>
+        <v>821.8541182771897</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>279.0679125332354</v>
+        <v>279.0679125332355</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>560.6457744410619</v>
@@ -33188,34 +33218,34 @@
         <v>7069.112073998887</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5816.280603427482</v>
+        <v>5816.280603427483</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.396351492128</v>
+        <v>901.3963514921277</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>300.6295457533571</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008076</v>
+        <v>571.6795744008077</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7589.986075073774</v>
+        <v>7589.986075073775</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.655996720889</v>
+        <v>6250.655996720888</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>987.1475980283611</v>
+        <v>987.1475980283614</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>321.7141332764122</v>
+        <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299143</v>
+        <v>593.5213632299141</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8153.039091255577</v>
+        <v>8153.039091255575</v>
       </c>
     </row>
     <row r="98">
@@ -33331,25 +33361,25 @@
         <v>151.8055148266722</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>6975.373307971806</v>
+        <v>6975.373307971811</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>10011.78106812466</v>
+        <v>10011.78106812467</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2639.658250704873</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>448.277386801492</v>
+        <v>448.2773868014629</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578742</v>
+        <v>7864.526914578741</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>11117.97029900591</v>
+        <v>11117.97029900588</v>
       </c>
     </row>
     <row r="100">
@@ -33582,40 +33612,40 @@
         <v>1135895.03984975</v>
       </c>
       <c r="K103" s="140" t="n">
-        <v>255058.7667674547</v>
+        <v>255058.7667674541</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58662.13438966972</v>
+        <v>58662.13438966971</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>4571.431810842299</v>
+        <v>4571.431810842301</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>1454187.372817716</v>
       </c>
       <c r="P103" s="139" t="n">
-        <v>1148419.705411591</v>
+        <v>1148419.705411597</v>
       </c>
       <c r="Q103" s="140" t="n">
-        <v>256655.8101514264</v>
+        <v>256655.8101514261</v>
       </c>
       <c r="R103" s="140" t="n">
-        <v>59175.12405820967</v>
+        <v>59175.12405820965</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>4844.630784977365</v>
+        <v>4844.630784977364</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>1469095.270406205</v>
+        <v>1469095.27040621</v>
       </c>
       <c r="V103" s="139" t="n">
-        <v>1159695.954534212</v>
+        <v>1159695.95453421</v>
       </c>
       <c r="W103" s="140" t="n">
-        <v>257981.4291505639</v>
+        <v>257981.4291505645</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>59655.70951589625</v>
+        <v>59655.70951589627</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>5336.818379074632</v>
@@ -33646,13 +33676,13 @@
         <v>48702</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1147367.644204108</v>
+        <v>1147367.644204109</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>257480.6278357828</v>
+        <v>257480.6278357822</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>59776.58186997884</v>
+        <v>59776.58186997882</v>
       </c>
       <c r="M104" s="143" t="n">
         <v>15819.80035996352</v>
@@ -33661,34 +33691,34 @@
         <v>1480444.654269833</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1160502.468979224</v>
+        <v>1160502.468979229</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>259202.0803003974</v>
+        <v>259202.0803003971</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>60373.31814510459</v>
+        <v>60373.31814510457</v>
       </c>
       <c r="S104" s="143" t="n">
         <v>17266.31177103306</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1497344.179195759</v>
+        <v>1497344.179195764</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1172449.016554634</v>
+        <v>1172449.016554633</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>260673.2307205008</v>
+        <v>260673.2307205013</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>60950.03499272167</v>
+        <v>60950.03499272169</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>19213.06972117535</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1513285.351989032</v>
+        <v>1513285.351989031</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
